--- a/storage/app/pdfs/ghg_asia_download.xlsx
+++ b/storage/app/pdfs/ghg_asia_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodrigofavela/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodrigofavela/Desktop/Cambio EthTool/Vietnam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D959BECF-24C2-5B44-8479-9BCE34316C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502085D9-ECB0-4148-96CB-83DF2292C891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="4140" windowWidth="23280" windowHeight="12480" tabRatio="853" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="5520" yWindow="4140" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -10097,7 +10097,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W111"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -10138,7 +10138,7 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
@@ -10169,8 +10169,15 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
-    </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+    </row>
+    <row r="6" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>18</v>
       </c>
@@ -10178,22 +10185,22 @@
         <v>19</v>
       </c>
       <c r="C6" s="23">
-        <v>48.283108136252032</v>
+        <v>48.949325901782046</v>
       </c>
       <c r="D6" s="23">
-        <v>41.909095364152577</v>
+        <v>42.459046339124036</v>
       </c>
       <c r="E6" s="23">
-        <v>40.344893885623236</v>
+        <v>40.833629488308716</v>
       </c>
       <c r="F6" s="23">
-        <v>39.085918227964541</v>
+        <v>39.511235956118341</v>
       </c>
       <c r="G6" s="23">
-        <v>37.919988167232162</v>
+        <v>38.279564473435236</v>
       </c>
       <c r="H6" s="23">
-        <v>36.319930400557901</v>
+        <v>36.61131165682395</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -10209,7 +10216,7 @@
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>20</v>
       </c>
@@ -10217,22 +10224,22 @@
         <v>19</v>
       </c>
       <c r="C7" s="23">
-        <v>71.368566639406922</v>
+        <v>75.026221645356188</v>
       </c>
       <c r="D7" s="23">
-        <v>64.381372523284568</v>
+        <v>67.84330407519208</v>
       </c>
       <c r="E7" s="23">
-        <v>62.534364542885932</v>
+        <v>65.898434367772566</v>
       </c>
       <c r="F7" s="23">
-        <v>61.009579488799346</v>
+        <v>64.275787586665103</v>
       </c>
       <c r="G7" s="23">
-        <v>59.595771264424748</v>
+        <v>62.764117635269635</v>
       </c>
       <c r="H7" s="23">
-        <v>57.766770421996732</v>
+        <v>60.837255065820749</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
@@ -10248,7 +10255,7 @@
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
     </row>
-    <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>21</v>
       </c>
@@ -10287,7 +10294,7 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>18</v>
       </c>
@@ -10298,19 +10305,19 @@
         <v>0</v>
       </c>
       <c r="D9" s="25">
-        <v>0.13201330689218213</v>
+        <v>0.13259180679384444</v>
       </c>
       <c r="E9" s="25">
-        <v>0.16440976061913065</v>
+        <v>0.16579791986834838</v>
       </c>
       <c r="F9" s="25">
-        <v>0.19048462833696567</v>
+        <v>0.19281348152988767</v>
       </c>
       <c r="G9" s="25">
-        <v>0.21463241222532251</v>
+        <v>0.21797565608474226</v>
       </c>
       <c r="H9" s="26">
-        <v>0.24777149188355402</v>
+        <v>0.25205687754954187</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -10326,7 +10333,7 @@
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
     </row>
-    <row r="10" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>20</v>
       </c>
@@ -10337,19 +10344,19 @@
         <v>0</v>
       </c>
       <c r="D10" s="25">
-        <v>9.7902962678590472E-2</v>
+        <v>9.5738761897370586E-2</v>
       </c>
       <c r="E10" s="25">
-        <v>0.12378281521550259</v>
+        <v>0.12166129491006554</v>
       </c>
       <c r="F10" s="25">
-        <v>0.1451477539537378</v>
+        <v>0.14328902379634217</v>
       </c>
       <c r="G10" s="25">
-        <v>0.16495771078694604</v>
+        <v>0.1634375787714418</v>
       </c>
       <c r="H10" s="26">
-        <v>0.19058525143336438</v>
+        <v>0.18912010052439682</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -10365,7 +10372,7 @@
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
@@ -10404,7 +10411,7 @@
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
     </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>18</v>
       </c>
@@ -10415,19 +10422,19 @@
         <v>0</v>
       </c>
       <c r="D12" s="25">
-        <v>4.0001278623531845E-2</v>
+        <v>4.07309320538096E-2</v>
       </c>
       <c r="E12" s="25">
-        <v>4.9817710030741515E-2</v>
+        <v>5.0931531684461358E-2</v>
       </c>
       <c r="F12" s="25">
-        <v>5.7718641180846825E-2</v>
+        <v>5.9230453262191493E-2</v>
       </c>
       <c r="G12" s="25">
-        <v>6.5035647732678004E-2</v>
+        <v>6.6960032086872373E-2</v>
       </c>
       <c r="H12" s="26">
-        <v>7.5077101809871774E-2</v>
+        <v>7.7429456626443821E-2</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
@@ -10443,7 +10450,7 @@
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>20</v>
       </c>
@@ -10454,19 +10461,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="27">
-        <v>4.3849409881814953E-2</v>
+        <v>4.5077708082369938E-2</v>
       </c>
       <c r="E13" s="27">
-        <v>5.5440645024489046E-2</v>
+        <v>5.728309232532152E-2</v>
       </c>
       <c r="F13" s="27">
-        <v>6.5009711477649723E-2</v>
+        <v>6.7466307878759693E-2</v>
       </c>
       <c r="G13" s="27">
-        <v>7.3882322613761625E-2</v>
+        <v>7.6953068115149043E-2</v>
       </c>
       <c r="H13" s="28">
-        <v>8.5360550680841502E-2</v>
+        <v>8.9045445282506366E-2</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
@@ -10482,7 +10489,7 @@
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
     </row>
-    <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -10497,15 +10504,15 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-    </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q14" s="16"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+    </row>
+    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -10520,13 +10527,13 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -10543,15 +10550,8 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-    </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -10566,15 +10566,8 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-    </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -10589,15 +10582,8 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-    </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -10612,15 +10598,8 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-    </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -10635,15 +10614,9 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-    </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -10658,15 +10631,15 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
+      <c r="O21" s="9"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-    </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -10681,15 +10654,15 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
+      <c r="O22" s="9"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
       <c r="T22" s="12"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-    </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -10704,15 +10677,15 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
+      <c r="O23" s="9"/>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-    </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -10727,15 +10700,15 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-    </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O24" s="9"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+    </row>
+    <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -10750,15 +10723,15 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-    </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O25" s="9"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+    </row>
+    <row r="26" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -10773,8 +10746,15 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O26" s="9"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+    </row>
+    <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -10789,8 +10769,15 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O27" s="9"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+    </row>
+    <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -10805,8 +10792,15 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O28" s="9"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+    </row>
+    <row r="29" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -10821,8 +10815,15 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O29" s="9"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+    </row>
+    <row r="30" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -10837,9 +10838,14 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
-      <c r="O30" s="9"/>
-    </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+    </row>
+    <row r="31" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -10854,15 +10860,14 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
-      <c r="O31" s="9"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-    </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q31" s="13"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+    </row>
+    <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -10877,13 +10882,12 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
-      <c r="O32" s="9"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
     </row>
     <row r="33" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
@@ -10900,13 +10904,6 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
-      <c r="O33" s="9"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
     </row>
     <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
@@ -10923,13 +10920,6 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
-      <c r="O34" s="9"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="12"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="12"/>
     </row>
     <row r="35" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
@@ -10946,13 +10936,6 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
-      <c r="O35" s="9"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
     </row>
     <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
@@ -10969,13 +10952,6 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
-      <c r="O36" s="9"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
     </row>
     <row r="37" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
@@ -10992,13 +10968,13 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
-      <c r="O37" s="9"/>
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
       <c r="S37" s="12"/>
       <c r="T37" s="12"/>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
     </row>
     <row r="38" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
@@ -11015,13 +10991,6 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
-      <c r="O38" s="9"/>
-      <c r="Q38" s="12"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="12"/>
-      <c r="U38" s="12"/>
-      <c r="V38" s="12"/>
     </row>
     <row r="39" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
@@ -11038,13 +11007,6 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
-      <c r="O39" s="9"/>
-      <c r="Q39" s="12"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
-      <c r="U39" s="12"/>
-      <c r="V39" s="12"/>
     </row>
     <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
@@ -11061,12 +11023,6 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
-      <c r="Q40" s="12"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="12"/>
     </row>
     <row r="41" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
@@ -11083,14 +11039,8 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="16"/>
-    </row>
-    <row r="42" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -11105,12 +11055,6 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="15"/>
     </row>
     <row r="43" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
@@ -11128,7 +11072,7 @@
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -11143,8 +11087,15 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q44" s="12"/>
+      <c r="R44" s="12"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="12"/>
+      <c r="U44" s="12"/>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
+    </row>
+    <row r="45" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -11159,8 +11110,15 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q45" s="12"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+    </row>
+    <row r="46" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -11175,8 +11133,15 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="12"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+    </row>
+    <row r="47" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -11199,7 +11164,7 @@
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
     </row>
-    <row r="48" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -11214,8 +11179,15 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q48" s="12"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="12"/>
+      <c r="T48" s="12"/>
+      <c r="U48" s="12"/>
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
+    </row>
+    <row r="49" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -11230,8 +11202,15 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q49" s="12"/>
+      <c r="R49" s="12"/>
+      <c r="S49" s="12"/>
+      <c r="T49" s="12"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+    </row>
+    <row r="50" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -11246,8 +11225,15 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q50" s="12"/>
+      <c r="R50" s="12"/>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12"/>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+    </row>
+    <row r="51" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -11262,8 +11248,15 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q51" s="12"/>
+      <c r="R51" s="12"/>
+      <c r="S51" s="12"/>
+      <c r="T51" s="12"/>
+      <c r="U51" s="12"/>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+    </row>
+    <row r="52" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -11278,8 +11271,15 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12"/>
+      <c r="S52" s="12"/>
+      <c r="T52" s="12"/>
+      <c r="U52" s="12"/>
+      <c r="V52" s="12"/>
+      <c r="W52" s="12"/>
+    </row>
+    <row r="53" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -11294,8 +11294,15 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q53" s="12"/>
+      <c r="R53" s="12"/>
+      <c r="S53" s="12"/>
+      <c r="T53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+    </row>
+    <row r="54" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -11318,7 +11325,7 @@
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
     </row>
-    <row r="55" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -11341,7 +11348,7 @@
       <c r="V55" s="12"/>
       <c r="W55" s="12"/>
     </row>
-    <row r="56" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -11364,7 +11371,7 @@
       <c r="V56" s="12"/>
       <c r="W56" s="12"/>
     </row>
-    <row r="57" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -11387,7 +11394,7 @@
       <c r="V57" s="12"/>
       <c r="W57" s="12"/>
     </row>
-    <row r="58" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -11410,7 +11417,7 @@
       <c r="V58" s="12"/>
       <c r="W58" s="12"/>
     </row>
-    <row r="59" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -11433,7 +11440,7 @@
       <c r="V59" s="12"/>
       <c r="W59" s="12"/>
     </row>
-    <row r="60" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -11456,7 +11463,7 @@
       <c r="V60" s="12"/>
       <c r="W60" s="12"/>
     </row>
-    <row r="61" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -11479,7 +11486,7 @@
       <c r="V61" s="12"/>
       <c r="W61" s="12"/>
     </row>
-    <row r="62" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -11494,15 +11501,15 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="12"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="12"/>
-      <c r="W62" s="12"/>
-    </row>
-    <row r="63" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q62" s="16"/>
+      <c r="R62" s="13"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="13"/>
+      <c r="U62" s="13"/>
+      <c r="V62" s="13"/>
+      <c r="W62" s="13"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -11517,13 +11524,13 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="12"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="12"/>
-      <c r="W63" s="12"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
     </row>
     <row r="64" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="17"/>
@@ -11540,15 +11547,8 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="12"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12"/>
-      <c r="U64" s="12"/>
-      <c r="V64" s="12"/>
-      <c r="W64" s="12"/>
-    </row>
-    <row r="65" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -11563,15 +11563,8 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" s="17"/>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12"/>
-      <c r="U65" s="12"/>
-      <c r="V65" s="12"/>
-      <c r="W65" s="12"/>
-    </row>
-    <row r="66" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -11586,15 +11579,8 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="12"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-      <c r="U66" s="12"/>
-      <c r="V66" s="12"/>
-      <c r="W66" s="12"/>
-    </row>
-    <row r="67" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -11609,15 +11595,8 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12"/>
-      <c r="U67" s="12"/>
-      <c r="V67" s="12"/>
-      <c r="W67" s="12"/>
-    </row>
-    <row r="68" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -11632,15 +11611,9 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" s="17"/>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="12"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="12"/>
-      <c r="W68" s="12"/>
-    </row>
-    <row r="69" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O68" s="9"/>
+    </row>
+    <row r="69" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -11655,15 +11628,15 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" s="17"/>
+      <c r="O69" s="9"/>
       <c r="Q69" s="12"/>
       <c r="R69" s="12"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12"/>
       <c r="U69" s="12"/>
       <c r="V69" s="12"/>
-      <c r="W69" s="12"/>
-    </row>
-    <row r="70" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -11678,15 +11651,15 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" s="17"/>
+      <c r="O70" s="9"/>
       <c r="Q70" s="12"/>
       <c r="R70" s="12"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12"/>
       <c r="U70" s="12"/>
       <c r="V70" s="12"/>
-      <c r="W70" s="12"/>
-    </row>
-    <row r="71" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -11701,15 +11674,15 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" s="17"/>
+      <c r="O71" s="9"/>
       <c r="Q71" s="12"/>
       <c r="R71" s="12"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12"/>
       <c r="U71" s="12"/>
       <c r="V71" s="12"/>
-      <c r="W71" s="12"/>
-    </row>
-    <row r="72" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -11724,15 +11697,15 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
-      <c r="Q72" s="16"/>
-      <c r="R72" s="13"/>
-      <c r="S72" s="13"/>
-      <c r="T72" s="13"/>
-      <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="W72" s="13"/>
-    </row>
-    <row r="73" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O72" s="9"/>
+      <c r="Q72" s="12"/>
+      <c r="R72" s="12"/>
+      <c r="S72" s="12"/>
+      <c r="T72" s="12"/>
+      <c r="U72" s="12"/>
+      <c r="V72" s="12"/>
+    </row>
+    <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -11747,15 +11720,15 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" s="17"/>
-      <c r="Q73" s="15"/>
-      <c r="R73" s="14"/>
-      <c r="S73" s="14"/>
-      <c r="T73" s="14"/>
-      <c r="U73" s="14"/>
-      <c r="V73" s="14"/>
-      <c r="W73" s="14"/>
-    </row>
-    <row r="74" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O73" s="9"/>
+      <c r="Q73" s="12"/>
+      <c r="R73" s="12"/>
+      <c r="S73" s="12"/>
+      <c r="T73" s="12"/>
+      <c r="U73" s="12"/>
+      <c r="V73" s="12"/>
+    </row>
+    <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -11770,8 +11743,15 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O74" s="9"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12"/>
+      <c r="S74" s="12"/>
+      <c r="T74" s="12"/>
+      <c r="U74" s="12"/>
+      <c r="V74" s="12"/>
+    </row>
+    <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -11786,8 +11766,15 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" s="17"/>
-    </row>
-    <row r="76" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O75" s="9"/>
+      <c r="Q75" s="12"/>
+      <c r="R75" s="12"/>
+      <c r="S75" s="12"/>
+      <c r="T75" s="12"/>
+      <c r="U75" s="12"/>
+      <c r="V75" s="12"/>
+    </row>
+    <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -11802,8 +11789,15 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" s="17"/>
-    </row>
-    <row r="77" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O76" s="9"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12"/>
+      <c r="S76" s="12"/>
+      <c r="T76" s="12"/>
+      <c r="U76" s="12"/>
+      <c r="V76" s="12"/>
+    </row>
+    <row r="77" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -11818,8 +11812,15 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" s="17"/>
-    </row>
-    <row r="78" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="O77" s="9"/>
+      <c r="Q77" s="12"/>
+      <c r="R77" s="12"/>
+      <c r="S77" s="12"/>
+      <c r="T77" s="12"/>
+      <c r="U77" s="12"/>
+      <c r="V77" s="12"/>
+    </row>
+    <row r="78" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="17"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -11834,9 +11835,14 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" s="17"/>
-      <c r="O78" s="9"/>
-    </row>
-    <row r="79" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q78" s="12"/>
+      <c r="R78" s="12"/>
+      <c r="S78" s="12"/>
+      <c r="T78" s="12"/>
+      <c r="U78" s="12"/>
+      <c r="V78" s="12"/>
+    </row>
+    <row r="79" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="17"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
@@ -11851,15 +11857,14 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" s="17"/>
-      <c r="O79" s="9"/>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="12"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12"/>
-      <c r="U79" s="12"/>
-      <c r="V79" s="12"/>
-    </row>
-    <row r="80" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="Q79" s="13"/>
+      <c r="R79" s="16"/>
+      <c r="S79" s="16"/>
+      <c r="T79" s="16"/>
+      <c r="U79" s="16"/>
+      <c r="V79" s="16"/>
+    </row>
+    <row r="80" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="17"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -11874,13 +11879,12 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" s="17"/>
-      <c r="O80" s="9"/>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12"/>
-      <c r="U80" s="12"/>
-      <c r="V80" s="12"/>
+      <c r="Q80" s="14"/>
+      <c r="R80" s="15"/>
+      <c r="S80" s="15"/>
+      <c r="T80" s="15"/>
+      <c r="U80" s="15"/>
+      <c r="V80" s="15"/>
     </row>
     <row r="81" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="17"/>
@@ -11897,13 +11901,6 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" s="17"/>
-      <c r="O81" s="9"/>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12"/>
-      <c r="U81" s="12"/>
-      <c r="V81" s="12"/>
     </row>
     <row r="82" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="17"/>
@@ -11920,13 +11917,6 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" s="17"/>
-      <c r="O82" s="9"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12"/>
-      <c r="S82" s="12"/>
-      <c r="T82" s="12"/>
-      <c r="U82" s="12"/>
-      <c r="V82" s="12"/>
     </row>
     <row r="83" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="17"/>
@@ -11943,13 +11933,6 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" s="17"/>
-      <c r="O83" s="9"/>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="12"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12"/>
-      <c r="U83" s="12"/>
-      <c r="V83" s="12"/>
     </row>
     <row r="84" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="17"/>
@@ -11966,13 +11949,6 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="17"/>
-      <c r="O84" s="9"/>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="12"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12"/>
-      <c r="U84" s="12"/>
-      <c r="V84" s="12"/>
     </row>
     <row r="85" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="17"/>
@@ -11989,13 +11965,13 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="17"/>
-      <c r="O85" s="9"/>
       <c r="Q85" s="12"/>
       <c r="R85" s="12"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12"/>
       <c r="U85" s="12"/>
       <c r="V85" s="12"/>
+      <c r="W85" s="12"/>
     </row>
     <row r="86" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="17"/>
@@ -12012,205 +11988,166 @@
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" s="17"/>
-      <c r="O86" s="9"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="12"/>
-      <c r="V86" s="12"/>
-    </row>
-    <row r="87" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-      <c r="K87" s="17"/>
-      <c r="L87" s="17"/>
-      <c r="M87" s="17"/>
-      <c r="N87" s="17"/>
-      <c r="O87" s="9"/>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="12"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12"/>
-      <c r="U87" s="12"/>
-      <c r="V87" s="12"/>
-    </row>
-    <row r="88" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17"/>
-      <c r="L88" s="17"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17"/>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="12"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12"/>
-      <c r="U88" s="12"/>
-      <c r="V88" s="12"/>
-    </row>
-    <row r="89" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="17"/>
-      <c r="L89" s="17"/>
-      <c r="M89" s="17"/>
-      <c r="N89" s="17"/>
-      <c r="Q89" s="13"/>
-      <c r="R89" s="16"/>
-      <c r="S89" s="16"/>
-      <c r="T89" s="16"/>
-      <c r="U89" s="16"/>
-      <c r="V89" s="16"/>
-    </row>
-    <row r="90" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="17"/>
-      <c r="G90" s="17"/>
-      <c r="H90" s="17"/>
-      <c r="I90" s="17"/>
-      <c r="J90" s="17"/>
-      <c r="K90" s="17"/>
-      <c r="L90" s="17"/>
-      <c r="M90" s="17"/>
-      <c r="N90" s="17"/>
-      <c r="Q90" s="14"/>
-      <c r="R90" s="15"/>
-      <c r="S90" s="15"/>
-      <c r="T90" s="15"/>
-      <c r="U90" s="15"/>
-      <c r="V90" s="15"/>
-    </row>
-    <row r="91" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="17"/>
-      <c r="M91" s="17"/>
-      <c r="N91" s="17"/>
-    </row>
-    <row r="92" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-      <c r="J92" s="17"/>
-      <c r="K92" s="17"/>
-      <c r="L92" s="17"/>
-      <c r="M92" s="17"/>
-      <c r="N92" s="17"/>
-    </row>
-    <row r="93" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="17"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17"/>
-      <c r="K93" s="17"/>
-      <c r="L93" s="17"/>
-      <c r="M93" s="17"/>
-      <c r="N93" s="17"/>
-    </row>
-    <row r="94" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="17"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="17"/>
-      <c r="I94" s="17"/>
-      <c r="J94" s="17"/>
-      <c r="K94" s="17"/>
-      <c r="L94" s="17"/>
-      <c r="M94" s="17"/>
-      <c r="N94" s="17"/>
-    </row>
-    <row r="95" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="17"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-      <c r="J95" s="17"/>
-      <c r="K95" s="17"/>
-      <c r="L95" s="17"/>
-      <c r="M95" s="17"/>
-      <c r="N95" s="17"/>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="12"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12"/>
-      <c r="U95" s="12"/>
-      <c r="V95" s="12"/>
-      <c r="W95" s="12"/>
-    </row>
-    <row r="96" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="17"/>
-      <c r="F96" s="17"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
-      <c r="L96" s="17"/>
-      <c r="M96" s="17"/>
-      <c r="N96" s="17"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A97" s="1"/>
@@ -12292,166 +12229,6 @@
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="1"/>
-      <c r="M102" s="1"/>
-      <c r="N102" s="1"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
-      <c r="N103" s="1"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-      <c r="N104" s="1"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
-      <c r="N105" s="1"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
-      <c r="N106" s="1"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="N107" s="1"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-      <c r="N108" s="1"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
-      <c r="N109" s="1"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
-      <c r="N110" s="1"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
-      <c r="K111" s="1"/>
-      <c r="L111" s="1"/>
-      <c r="M111" s="1"/>
-      <c r="N111" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Contenido!A1" display="Contenido" xr:uid="{6106CCAC-85D3-4A58-8C19-CA66F038BC49}"/>

--- a/storage/app/pdfs/ghg_asia_download.xlsx
+++ b/storage/app/pdfs/ghg_asia_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Entregables/Asia/1. Informacion AsiaAfrica/4. GHG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/ssantos_faro90_com/Documents/Escritorio/Archivos faltantes emisioens y GHG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{D959BECF-24C2-5B44-8479-9BCE34316C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5943B48-D6CE-FB40-8064-8A2EC71CC372}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{D959BECF-24C2-5B44-8479-9BCE34316C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8623735B-053C-44D4-81F6-CFBF8DF23C8A}"/>
   <bookViews>
-    <workbookView xWindow="9280" yWindow="900" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="27">
   <si>
     <t>Content</t>
   </si>
@@ -129,13 +129,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,16 +204,10 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -221,8 +216,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,13 +258,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD18316"/>
-        <bgColor theme="4"/>
+        <bgColor rgb="FF4F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002F60"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -265,26 +279,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -301,17 +295,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -375,12 +358,43 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF95B3D7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color rgb="FF95B3D7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -398,7 +412,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -440,49 +454,50 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="5" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="5" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="7" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="5" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hipervínculo" xfId="4" builtinId="8"/>
@@ -884,135 +899,135 @@
     <tabColor rgb="FF002F60"/>
   </sheetPr>
   <dimension ref="A1:A35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="5"/>
+    <col min="1" max="1" width="80.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:1" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
     </row>
   </sheetData>
@@ -1038,30 +1053,30 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="5" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="5"/>
+    <col min="3" max="8" width="10.77734375" style="5"/>
     <col min="9" max="9" width="16" style="5" customWidth="1"/>
-    <col min="10" max="10" width="14.1640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" style="5" customWidth="1"/>
     <col min="11" max="14" width="12" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.33203125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="31.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.44140625" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="5"/>
+    <col min="18" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B3"/>
@@ -1085,29 +1100,29 @@
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
     </row>
-    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="16"/>
@@ -1124,30 +1139,30 @@
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
     </row>
-    <row r="5" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>221.89754147692614</v>
-      </c>
-      <c r="D5" s="22">
-        <v>203.41945554100403</v>
-      </c>
-      <c r="E5" s="22">
-        <v>197.10893262918972</v>
-      </c>
-      <c r="F5" s="22">
-        <v>191.1231523399216</v>
-      </c>
-      <c r="G5" s="22">
-        <v>186.22954525455896</v>
-      </c>
-      <c r="H5" s="22">
-        <v>179.22958080980786</v>
+      <c r="C5" s="24">
+        <v>238.41343135687046</v>
+      </c>
+      <c r="D5" s="24">
+        <v>218.27298411589348</v>
+      </c>
+      <c r="E5" s="24">
+        <v>211.56821606237247</v>
+      </c>
+      <c r="F5" s="24">
+        <v>205.08497234830304</v>
+      </c>
+      <c r="G5" s="24">
+        <v>199.83456978490372</v>
+      </c>
+      <c r="H5" s="24">
+        <v>192.323467850052</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -1162,30 +1177,30 @@
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
     </row>
-    <row r="6" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>329.71472966808733</v>
-      </c>
-      <c r="D6" s="22">
-        <v>307.32665467591187</v>
-      </c>
-      <c r="E6" s="22">
-        <v>299.17221765258216</v>
-      </c>
-      <c r="F6" s="22">
-        <v>291.42190569576547</v>
-      </c>
-      <c r="G6" s="22">
-        <v>284.84751208915452</v>
-      </c>
-      <c r="H6" s="22">
-        <v>276.25519462487694</v>
+      <c r="C6" s="24">
+        <v>345.61663694229799</v>
+      </c>
+      <c r="D6" s="24">
+        <v>321.58846671701264</v>
+      </c>
+      <c r="E6" s="24">
+        <v>313.05028502235496</v>
+      </c>
+      <c r="F6" s="24">
+        <v>304.81255805481004</v>
+      </c>
+      <c r="G6" s="24">
+        <v>297.89094048380804</v>
+      </c>
+      <c r="H6" s="24">
+        <v>288.79655344404131</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -1200,29 +1215,29 @@
       <c r="U6" s="15"/>
       <c r="V6" s="15"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -1238,30 +1253,30 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
     </row>
-    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>8.3273053919092385E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.11171195806292446</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.13868738216824536</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.1607408355449314</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.1922867661494802</v>
+      <c r="D8" s="26">
+        <v>8.4476982384560556E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.11259942504797299</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.13979270722663076</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.16181496718706154</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.19331949229751427</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -1270,30 +1285,30 @@
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>6.7901349189685212E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>9.2633143949168675E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.11613925774826604</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.13607889955083025</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.16213875278494927</v>
+      <c r="D9" s="26">
+        <v>6.9522608743215517E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>9.4226806348387995E-2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.11806167448559585</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.13808853902614052</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.16440204962628291</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -1302,29 +1317,29 @@
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -1334,30 +1349,30 @@
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>3.4747525357161753E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>4.6614287729390934E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>5.7870380655087331E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>6.7072672325138458E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>8.0235910275578359E-2</v>
+      <c r="D11" s="26">
+        <v>3.7873549437819655E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>5.0481678805845739E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>6.2673237830546485E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>7.2546473448114296E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <v>8.667089119606447E-2</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -1366,30 +1381,30 @@
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>4.2100150750805282E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>5.7434342193799441E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>7.2008587717891537E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>8.4371551573881209E-2</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0.10052916497616297</v>
+      <c r="D12" s="28">
+        <v>4.518430410404068E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>6.1240116701081017E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>7.6730932561704296E-2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>8.9746841400693375E-2</v>
+      </c>
+      <c r="H12" s="29">
+        <v>0.10684858263990944</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -1405,15 +1420,31 @@
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -1421,15 +1452,31 @@
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="31">
+        <v>170.97316689231261</v>
+      </c>
+      <c r="D14" s="31">
+        <v>156.52986968451822</v>
+      </c>
+      <c r="E14" s="31">
+        <v>151.72168660160708</v>
+      </c>
+      <c r="F14" s="31">
+        <v>147.07236502932565</v>
+      </c>
+      <c r="G14" s="31">
+        <v>143.30714950176505</v>
+      </c>
+      <c r="H14" s="31">
+        <v>137.92072107219255</v>
+      </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
@@ -1437,15 +1484,31 @@
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31">
+        <v>247.85168609164631</v>
+      </c>
+      <c r="D15" s="31">
+        <v>230.62039029315054</v>
+      </c>
+      <c r="E15" s="31">
+        <v>224.49741326316735</v>
+      </c>
+      <c r="F15" s="31">
+        <v>218.58990100758831</v>
+      </c>
+      <c r="G15" s="31">
+        <v>213.6262088640853</v>
+      </c>
+      <c r="H15" s="31">
+        <v>207.10436089484961</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -1453,7 +1516,7 @@
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1469,7 +1532,7 @@
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1485,7 +1548,7 @@
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -1501,7 +1564,7 @@
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -1524,7 +1587,7 @@
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
     </row>
-    <row r="20" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -1547,7 +1610,7 @@
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
     </row>
-    <row r="21" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -1570,7 +1633,7 @@
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
     </row>
-    <row r="22" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1593,7 +1656,7 @@
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
     </row>
-    <row r="23" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -1616,7 +1679,7 @@
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
     </row>
-    <row r="24" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -1639,7 +1702,7 @@
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
     </row>
-    <row r="25" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -1662,7 +1725,7 @@
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
     </row>
-    <row r="26" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -1685,7 +1748,7 @@
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
     </row>
-    <row r="27" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -1708,7 +1771,7 @@
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
     </row>
-    <row r="28" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -1731,7 +1794,7 @@
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -1754,7 +1817,7 @@
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -1777,7 +1840,7 @@
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -1800,7 +1863,7 @@
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -1823,7 +1886,7 @@
       <c r="V32" s="11"/>
       <c r="W32" s="11"/>
     </row>
-    <row r="33" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -1846,7 +1909,7 @@
       <c r="V33" s="11"/>
       <c r="W33" s="11"/>
     </row>
-    <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -1869,7 +1932,7 @@
       <c r="V34" s="11"/>
       <c r="W34" s="11"/>
     </row>
-    <row r="35" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -1892,7 +1955,7 @@
       <c r="V35" s="11"/>
       <c r="W35" s="11"/>
     </row>
-    <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -1915,7 +1978,7 @@
       <c r="V36" s="11"/>
       <c r="W36" s="11"/>
     </row>
-    <row r="37" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -1938,7 +2001,7 @@
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
     </row>
-    <row r="38" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -1961,7 +2024,7 @@
       <c r="V38" s="13"/>
       <c r="W38" s="13"/>
     </row>
-    <row r="39" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -1977,7 +2040,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -1993,7 +2056,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -2009,7 +2072,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -2025,7 +2088,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -2042,7 +2105,7 @@
       <c r="N43" s="16"/>
       <c r="O43" s="8"/>
     </row>
-    <row r="44" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -2065,7 +2128,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
     </row>
-    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -2088,7 +2151,7 @@
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
     </row>
-    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -2111,7 +2174,7 @@
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
     </row>
-    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -2134,7 +2197,7 @@
       <c r="U47" s="11"/>
       <c r="V47" s="11"/>
     </row>
-    <row r="48" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -2157,7 +2220,7 @@
       <c r="U48" s="11"/>
       <c r="V48" s="11"/>
     </row>
-    <row r="49" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -2180,7 +2243,7 @@
       <c r="U49" s="11"/>
       <c r="V49" s="11"/>
     </row>
-    <row r="50" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -2203,7 +2266,7 @@
       <c r="U50" s="11"/>
       <c r="V50" s="11"/>
     </row>
-    <row r="51" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -2226,7 +2289,7 @@
       <c r="U51" s="11"/>
       <c r="V51" s="11"/>
     </row>
-    <row r="52" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -2249,7 +2312,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -2271,7 +2334,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -2293,7 +2356,7 @@
       <c r="U54" s="15"/>
       <c r="V54" s="15"/>
     </row>
-    <row r="55" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -2315,7 +2378,7 @@
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
     </row>
-    <row r="56" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -2331,7 +2394,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -2347,7 +2410,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -2363,7 +2426,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -2379,7 +2442,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -2402,7 +2465,7 @@
       <c r="V60" s="11"/>
       <c r="W60" s="11"/>
     </row>
-    <row r="61" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -2418,7 +2481,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -2433,7 +2496,7 @@
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -2448,7 +2511,7 @@
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -2463,7 +2526,7 @@
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -2478,7 +2541,7 @@
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -2493,7 +2556,7 @@
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -2508,7 +2571,7 @@
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -2523,7 +2586,7 @@
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -2538,7 +2601,7 @@
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -2553,7 +2616,7 @@
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -2582,27 +2645,27 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="12.44140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B3"/>
@@ -2624,29 +2687,29 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
     </row>
-    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="16"/>
@@ -2654,60 +2717,60 @@
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>54.355384656205217</v>
-      </c>
-      <c r="D5" s="22">
-        <v>49.39774130099719</v>
-      </c>
-      <c r="E5" s="22">
-        <v>47.613619983417614</v>
-      </c>
-      <c r="F5" s="22">
-        <v>45.85425420505608</v>
-      </c>
-      <c r="G5" s="22">
-        <v>44.34669348071219</v>
-      </c>
-      <c r="H5" s="22">
-        <v>42.344766859465693</v>
+      <c r="C5" s="24">
+        <v>60.363313285803542</v>
+      </c>
+      <c r="D5" s="24">
+        <v>55.008037144020335</v>
+      </c>
+      <c r="E5" s="24">
+        <v>52.385183512723977</v>
+      </c>
+      <c r="F5" s="24">
+        <v>49.583425403533319</v>
+      </c>
+      <c r="G5" s="24">
+        <v>47.240149113406879</v>
+      </c>
+      <c r="H5" s="24">
+        <v>44.458214627305686</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>95.646561721098934</v>
-      </c>
-      <c r="D6" s="22">
-        <v>89.127042747530226</v>
-      </c>
-      <c r="E6" s="22">
-        <v>86.604524529392364</v>
-      </c>
-      <c r="F6" s="22">
-        <v>84.13716326053229</v>
-      </c>
-      <c r="G6" s="22">
-        <v>81.953679257201046</v>
-      </c>
-      <c r="H6" s="22">
-        <v>79.309697086587335</v>
+      <c r="C6" s="24">
+        <v>103.34712783269113</v>
+      </c>
+      <c r="D6" s="24">
+        <v>96.365950549378084</v>
+      </c>
+      <c r="E6" s="24">
+        <v>92.974431123311263</v>
+      </c>
+      <c r="F6" s="24">
+        <v>89.435654865769123</v>
+      </c>
+      <c r="G6" s="24">
+        <v>86.388747365850463</v>
+      </c>
+      <c r="H6" s="24">
+        <v>82.938437729788603</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -2716,29 +2779,29 @@
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -2748,30 +2811,30 @@
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>9.1207952745893453E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.12403122000568829</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.15639904868520965</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.18413430865768757</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.22096463621232768</v>
+      <c r="D8" s="26">
+        <v>8.8717398868207592E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.132168519897265</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.17858343579038555</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.2174029796916899</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.26348949043256831</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -2781,30 +2844,30 @@
       <c r="N8" s="16"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>6.8162606749831031E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>9.4535935521370254E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.12033258962436653</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.1431612618112266</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.17080451550521136</v>
+      <c r="D9" s="26">
+        <v>6.7550762461583702E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>0.1003675373172658</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.13460918806997052</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.16409145394243196</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.1974770903739308</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -2820,29 +2883,29 @@
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -2859,30 +2922,30 @@
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>4.0529242454620952E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>5.5114617050532416E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>6.9497612576555984E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>8.1822075982704662E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>9.8188031255309144E-2</v>
+      <c r="D11" s="26">
+        <v>4.377993123159446E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>6.522202843976134E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>8.8126688087636254E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0.10728321188254206</v>
+      </c>
+      <c r="H11" s="27">
+        <v>0.13002581138026964</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -2898,30 +2961,30 @@
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>5.3297735685180266E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>7.3919580609081187E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>9.4090511820524705E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>0.11194071729644585</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0.13355554247864204</v>
+      <c r="D12" s="28">
+        <v>5.707183967496466E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>8.4797858523057323E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>0.11372771705834588</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.13863649809667544</v>
+      </c>
+      <c r="H12" s="29">
+        <v>0.16684313293590106</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -2937,15 +3000,31 @@
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -2960,15 +3039,31 @@
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="31">
+        <v>107.96254795664871</v>
+      </c>
+      <c r="D14" s="31">
+        <v>98.384391526750704</v>
+      </c>
+      <c r="E14" s="31">
+        <v>93.69329778888094</v>
+      </c>
+      <c r="F14" s="31">
+        <v>88.682225205866104</v>
+      </c>
+      <c r="G14" s="31">
+        <v>84.491168335766318</v>
+      </c>
+      <c r="H14" s="31">
+        <v>79.515551209749617</v>
+      </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
@@ -2983,15 +3078,31 @@
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31">
+        <v>184.84106715598242</v>
+      </c>
+      <c r="D15" s="31">
+        <v>172.35491213538302</v>
+      </c>
+      <c r="E15" s="31">
+        <v>166.28902445044116</v>
+      </c>
+      <c r="F15" s="31">
+        <v>159.95976118412875</v>
+      </c>
+      <c r="G15" s="31">
+        <v>154.51022769808657</v>
+      </c>
+      <c r="H15" s="31">
+        <v>148.33919103240669</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -3006,7 +3117,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -3029,7 +3140,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -3052,7 +3163,7 @@
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -3074,7 +3185,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3096,7 +3207,7 @@
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -3118,7 +3229,7 @@
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -3134,7 +3245,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -3150,7 +3261,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -3166,7 +3277,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -3182,7 +3293,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -3205,7 +3316,7 @@
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -3221,7 +3332,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -3237,7 +3348,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -3253,7 +3364,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -3269,7 +3380,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -3285,7 +3396,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -3301,7 +3412,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -3317,7 +3428,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -3333,7 +3444,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -3349,7 +3460,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -3365,7 +3476,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -3381,7 +3492,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -3397,7 +3508,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -3413,7 +3524,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -3429,7 +3540,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -3445,7 +3556,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -3461,7 +3572,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -3477,7 +3588,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -3493,7 +3604,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -3509,7 +3620,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -3525,7 +3636,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -3541,7 +3652,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -3557,7 +3668,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -3573,7 +3684,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -3589,7 +3700,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -3605,7 +3716,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -3621,7 +3732,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -3637,7 +3748,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -3653,7 +3764,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -3669,7 +3780,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -3685,7 +3796,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -3701,7 +3812,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -3717,7 +3828,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -3733,7 +3844,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -3749,7 +3860,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -3765,7 +3876,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -3781,7 +3892,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -3797,7 +3908,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -3813,7 +3924,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -3829,7 +3940,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -3845,7 +3956,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -3861,7 +3972,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -3877,7 +3988,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -3893,7 +4004,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -3909,7 +4020,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -3925,7 +4036,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -3941,7 +4052,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -3957,7 +4068,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -3973,7 +4084,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="16"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -4004,7 +4115,7 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" style="5" customWidth="1"/>
@@ -4012,28 +4123,28 @@
     <col min="4" max="7" width="12" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="5"/>
+    <col min="10" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -4041,29 +4152,29 @@
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="16"/>
@@ -4073,30 +4184,30 @@
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>76.331612229182355</v>
-      </c>
-      <c r="D5" s="22">
-        <v>69.994289906425976</v>
-      </c>
-      <c r="E5" s="22">
-        <v>67.830982807735523</v>
-      </c>
-      <c r="F5" s="22">
-        <v>65.785822087876923</v>
-      </c>
-      <c r="G5" s="22">
-        <v>64.127619567866347</v>
-      </c>
-      <c r="H5" s="22">
-        <v>61.731307263165263</v>
+      <c r="C5" s="24">
+        <v>81.110961888951806</v>
+      </c>
+      <c r="D5" s="24">
+        <v>74.432681711004292</v>
+      </c>
+      <c r="E5" s="24">
+        <v>71.184271396091575</v>
+      </c>
+      <c r="F5" s="24">
+        <v>67.714422632842727</v>
+      </c>
+      <c r="G5" s="24">
+        <v>64.915396830985244</v>
+      </c>
+      <c r="H5" s="24">
+        <v>61.503347997024072</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -4105,30 +4216,30 @@
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>113.50115927606072</v>
-      </c>
-      <c r="D6" s="22">
-        <v>106.22491137651369</v>
-      </c>
-      <c r="E6" s="22">
-        <v>103.63043602150091</v>
-      </c>
-      <c r="F6" s="22">
-        <v>101.18147382732603</v>
-      </c>
-      <c r="G6" s="22">
-        <v>99.148340639292485</v>
-      </c>
-      <c r="H6" s="22">
-        <v>96.407584764756663</v>
+      <c r="C6" s="24">
+        <v>119.05722566499713</v>
+      </c>
+      <c r="D6" s="24">
+        <v>111.42039956885374</v>
+      </c>
+      <c r="E6" s="24">
+        <v>107.73181105199447</v>
+      </c>
+      <c r="F6" s="24">
+        <v>103.84972274118701</v>
+      </c>
+      <c r="G6" s="24">
+        <v>100.66793149942292</v>
+      </c>
+      <c r="H6" s="24">
+        <v>96.904241400088566</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -4138,29 +4249,29 @@
       <c r="N6" s="16"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -4177,30 +4288,30 @@
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
     </row>
-    <row r="8" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>8.3023561767945411E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.1113644684449224</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.13815757106822471</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.15988123799447665</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.1912746834454421</v>
+      <c r="D8" s="26">
+        <v>8.2335112571968752E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.1223840805445109</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.16516311660130656</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.19967171737082523</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.24173815024869658</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -4216,30 +4327,30 @@
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
     </row>
-    <row r="9" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>6.4107256225018242E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>8.6965836450638836E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.10854237549037188</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.12645526026618728</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.15060264247811408</v>
+      <c r="D9" s="26">
+        <v>6.414416305677971E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>9.5125806516524095E-2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.12773271709355088</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.15445760694372263</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.18607005279328925</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -4255,29 +4366,29 @@
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -4294,30 +4405,30 @@
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>1.8110736694291439E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>2.4293014201715684E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>3.0137654162959854E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>3.4876448829894227E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>4.1724606297266958E-2</v>
+      <c r="D11" s="26">
+        <v>1.9085122661223166E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>2.836839734604563E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>3.8284496625793189E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>4.6283524719399838E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <v>5.6034443936186291E-2</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -4333,30 +4444,30 @@
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>2.0793988867804866E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>2.8208454729157426E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>3.5207074526940517E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>4.1017342327377339E-2</v>
-      </c>
-      <c r="H12" s="27">
-        <v>4.8849847202316596E-2</v>
+      <c r="D12" s="28">
+        <v>2.1824445651233686E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>3.2365657222964132E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>4.345985058102593E-2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>5.2552741941288721E-2</v>
+      </c>
+      <c r="H12" s="29">
+        <v>6.3308578068353327E-2</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -4372,15 +4483,31 @@
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
     </row>
-    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -4395,15 +4522,31 @@
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
     </row>
-    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="31">
+        <v>164.32950231038731</v>
+      </c>
+      <c r="D14" s="31">
+        <v>150.79941423876596</v>
+      </c>
+      <c r="E14" s="31">
+        <v>144.21818726379351</v>
+      </c>
+      <c r="F14" s="31">
+        <v>137.18832955926212</v>
+      </c>
+      <c r="G14" s="31">
+        <v>131.51754836937928</v>
+      </c>
+      <c r="H14" s="31">
+        <v>124.60479239058536</v>
+      </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
@@ -4418,15 +4561,31 @@
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
     </row>
-    <row r="15" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31">
+        <v>241.20802150972102</v>
+      </c>
+      <c r="D15" s="31">
+        <v>225.73593484739825</v>
+      </c>
+      <c r="E15" s="31">
+        <v>218.26291392535376</v>
+      </c>
+      <c r="F15" s="31">
+        <v>210.39786553752475</v>
+      </c>
+      <c r="G15" s="31">
+        <v>203.95160773169954</v>
+      </c>
+      <c r="H15" s="31">
+        <v>196.32643221324241</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -4441,7 +4600,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -4463,7 +4622,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -4485,7 +4644,7 @@
       <c r="U17" s="15"/>
       <c r="V17" s="15"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -4507,7 +4666,7 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4523,7 +4682,7 @@
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -4539,7 +4698,7 @@
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -4555,7 +4714,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -4571,7 +4730,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -4594,7 +4753,7 @@
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -4610,7 +4769,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -4626,7 +4785,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -4642,7 +4801,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4658,7 +4817,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -4674,7 +4833,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -4690,7 +4849,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -4706,7 +4865,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -4722,7 +4881,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -4738,7 +4897,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -4754,7 +4913,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -4770,7 +4929,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -4786,7 +4945,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -4802,7 +4961,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -4818,7 +4977,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -4834,7 +4993,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -4850,7 +5009,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -4866,7 +5025,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -4882,7 +5041,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -4898,7 +5057,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -4914,7 +5073,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -4930,7 +5089,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -4946,7 +5105,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -4962,7 +5121,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -4978,7 +5137,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -4994,7 +5153,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -5010,7 +5169,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -5026,7 +5185,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -5042,7 +5201,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -5058,7 +5217,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -5074,7 +5233,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -5090,7 +5249,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -5106,7 +5265,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -5122,7 +5281,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -5138,7 +5297,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -5154,7 +5313,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -5170,7 +5329,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -5186,7 +5345,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -5202,7 +5361,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -5218,7 +5377,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -5234,7 +5393,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -5250,7 +5409,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -5266,7 +5425,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -5282,7 +5441,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -5298,7 +5457,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -5314,7 +5473,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -5330,7 +5489,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -5346,7 +5505,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -5362,7 +5521,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -5392,36 +5551,36 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="5" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" style="5" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="5"/>
+    <col min="10" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -5429,29 +5588,29 @@
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="16"/>
@@ -5461,30 +5620,30 @@
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>41.913207513884856</v>
-      </c>
-      <c r="D5" s="22">
-        <v>38.189475303449193</v>
-      </c>
-      <c r="E5" s="22">
-        <v>36.965475043695726</v>
-      </c>
-      <c r="F5" s="22">
-        <v>35.730171672755993</v>
-      </c>
-      <c r="G5" s="22">
-        <v>34.721897314225998</v>
-      </c>
-      <c r="H5" s="22">
-        <v>33.324116988173721</v>
+      <c r="C5" s="24">
+        <v>44.231099453938725</v>
+      </c>
+      <c r="D5" s="24">
+        <v>40.292134749524841</v>
+      </c>
+      <c r="E5" s="24">
+        <v>39.002567919230067</v>
+      </c>
+      <c r="F5" s="24">
+        <v>37.696825304824358</v>
+      </c>
+      <c r="G5" s="24">
+        <v>36.630444098375698</v>
+      </c>
+      <c r="H5" s="24">
+        <v>35.155281627316249</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -5493,30 +5652,30 @@
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>63.606625824217517</v>
-      </c>
-      <c r="D6" s="22">
-        <v>59.135889366175689</v>
-      </c>
-      <c r="E6" s="22">
-        <v>57.560592560735707</v>
-      </c>
-      <c r="F6" s="22">
-        <v>55.989861625468812</v>
-      </c>
-      <c r="G6" s="22">
-        <v>54.662900811843926</v>
-      </c>
-      <c r="H6" s="22">
-        <v>52.96411236762161</v>
+      <c r="C6" s="24">
+        <v>67.164603951538581</v>
+      </c>
+      <c r="D6" s="24">
+        <v>62.435933123952672</v>
+      </c>
+      <c r="E6" s="24">
+        <v>60.774988173564381</v>
+      </c>
+      <c r="F6" s="24">
+        <v>59.114643557525227</v>
+      </c>
+      <c r="G6" s="24">
+        <v>57.711358450239437</v>
+      </c>
+      <c r="H6" s="24">
+        <v>55.917980982672098</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -5525,29 +5684,29 @@
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -5558,30 +5717,30 @@
       <c r="N7" s="16"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>8.8843885527063973E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.11804709693358743</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.14751998732334121</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.17157623160376229</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.20492563168461331</v>
+      <c r="D8" s="26">
+        <v>8.9054189315728713E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.1182093956347057</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.14773031260321742</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.17183962075096459</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.20519087109905168</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -5597,30 +5756,30 @@
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
     </row>
-    <row r="9" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>7.0287275894764467E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>9.5053513452993912E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.11974796807801595</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.14060995841990359</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.16731768614809761</v>
+      <c r="D9" s="26">
+        <v>7.0404209202183279E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>9.5133677592806359E-2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.11985420772854789</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.14074743161025655</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.16744866056206156</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -5636,29 +5795,29 @@
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -5675,30 +5834,30 @@
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>4.2549897656482288E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>5.6536157366045142E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>7.0651574114029711E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>8.2172802908322434E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>9.8144791885695873E-2</v>
+      <c r="D11" s="26">
+        <v>4.5009290564881371E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>5.9744758517292801E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>7.4665061984058548E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>8.6850259155333648E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <v>0.10370646916806156</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -5714,30 +5873,30 @@
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>5.1085676409724341E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>6.9086089452909491E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>8.70343297571331E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>0.1021970868038584</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0.12160859932860503</v>
+      <c r="D12" s="28">
+        <v>5.403301000031728E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>7.3012097017910407E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>9.1984324206796225E-2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.10801921455969039</v>
+      </c>
+      <c r="H12" s="29">
+        <v>0.12851156561828167</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -5753,15 +5912,31 @@
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
     </row>
-    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -5776,15 +5951,31 @@
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
     </row>
-    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="31">
+        <v>149.23741718856911</v>
+      </c>
+      <c r="D14" s="31">
+        <v>135.94719998526793</v>
+      </c>
+      <c r="E14" s="31">
+        <v>131.5961522966239</v>
+      </c>
+      <c r="F14" s="31">
+        <v>127.19052689520502</v>
+      </c>
+      <c r="G14" s="31">
+        <v>123.59251601703191</v>
+      </c>
+      <c r="H14" s="31">
+        <v>118.61526155507403</v>
+      </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
@@ -5799,15 +5990,31 @@
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
     </row>
-    <row r="15" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31">
+        <v>226.61593638790282</v>
+      </c>
+      <c r="D15" s="31">
+        <v>210.66122059390023</v>
+      </c>
+      <c r="E15" s="31">
+        <v>205.05712895818417</v>
+      </c>
+      <c r="F15" s="31">
+        <v>199.45506287346768</v>
+      </c>
+      <c r="G15" s="31">
+        <v>194.72032537935218</v>
+      </c>
+      <c r="H15" s="31">
+        <v>188.66940137773111</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -5822,7 +6029,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -5845,7 +6052,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -5867,7 +6074,7 @@
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -5889,7 +6096,7 @@
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5911,7 +6118,7 @@
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -5927,7 +6134,7 @@
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -5943,7 +6150,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -5959,7 +6166,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -5975,7 +6182,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -5998,7 +6205,7 @@
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -6014,7 +6221,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -6030,7 +6237,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -6046,7 +6253,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -6062,7 +6269,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -6078,7 +6285,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -6094,7 +6301,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -6110,7 +6317,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -6126,7 +6333,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -6142,7 +6349,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -6158,7 +6365,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -6174,7 +6381,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -6190,7 +6397,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -6206,7 +6413,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -6222,7 +6429,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -6238,7 +6445,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -6254,7 +6461,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -6270,7 +6477,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -6286,7 +6493,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -6302,7 +6509,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -6318,7 +6525,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -6334,7 +6541,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -6350,7 +6557,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -6366,7 +6573,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -6382,7 +6589,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -6398,7 +6605,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -6414,7 +6621,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -6430,7 +6637,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -6446,7 +6653,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -6462,7 +6669,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -6478,7 +6685,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -6494,7 +6701,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -6510,7 +6717,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -6526,7 +6733,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -6542,7 +6749,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -6558,7 +6765,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -6574,7 +6781,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -6590,7 +6797,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -6606,7 +6813,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -6622,7 +6829,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -6638,7 +6845,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -6654,7 +6861,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -6670,7 +6877,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -6686,7 +6893,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -6702,7 +6909,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -6718,7 +6925,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -6734,7 +6941,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -6750,7 +6957,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -6766,7 +6973,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -6796,36 +7003,36 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="8.77734375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -6840,29 +7047,29 @@
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
     </row>
-    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="16"/>
@@ -6879,30 +7086,30 @@
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
     </row>
-    <row r="5" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>61.964890631970007</v>
-      </c>
-      <c r="D5" s="22">
-        <v>56.81737345950949</v>
-      </c>
-      <c r="E5" s="22">
-        <v>55.069431862992424</v>
-      </c>
-      <c r="F5" s="22">
-        <v>53.410562114851572</v>
-      </c>
-      <c r="G5" s="22">
-        <v>52.093183598654093</v>
-      </c>
-      <c r="H5" s="22">
-        <v>50.152282329392655</v>
+      <c r="C5" s="24">
+        <v>53.3166269448893</v>
+      </c>
+      <c r="D5" s="24">
+        <v>48.941508429346207</v>
+      </c>
+      <c r="E5" s="24">
+        <v>47.387277052467788</v>
+      </c>
+      <c r="F5" s="24">
+        <v>45.954032769878822</v>
+      </c>
+      <c r="G5" s="24">
+        <v>44.786912384327643</v>
+      </c>
+      <c r="H5" s="24">
+        <v>43.088227074342647</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -6918,30 +7125,30 @@
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
     </row>
-    <row r="6" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>90.137747696717057</v>
-      </c>
-      <c r="D6" s="22">
-        <v>83.688567203575928</v>
-      </c>
-      <c r="E6" s="22">
-        <v>81.318819492203247</v>
-      </c>
-      <c r="F6" s="22">
-        <v>79.058886428057818</v>
-      </c>
-      <c r="G6" s="22">
-        <v>77.162327377962825</v>
-      </c>
-      <c r="H6" s="22">
-        <v>74.665353434000892</v>
+      <c r="C6" s="24">
+        <v>81.795618762270749</v>
+      </c>
+      <c r="D6" s="24">
+        <v>76.1046926602463</v>
+      </c>
+      <c r="E6" s="24">
+        <v>73.921898435933812</v>
+      </c>
+      <c r="F6" s="24">
+        <v>71.881059502263398</v>
+      </c>
+      <c r="G6" s="24">
+        <v>70.128465032640932</v>
+      </c>
+      <c r="H6" s="24">
+        <v>67.867664594741555</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -6957,29 +7164,29 @@
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -6996,30 +7203,30 @@
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
     </row>
-    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>8.307151227028424E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.1112800926242571</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.13805121625930761</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.15931129600384916</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.19063389254951393</v>
+      <c r="D8" s="26">
+        <v>8.2059176775481912E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.11121014648114146</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.13809189734791025</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.15998226161940798</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.19184259126368275</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -7035,30 +7242,30 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
     </row>
-    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>7.1548054593514279E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>9.7838346640150273E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.12291034058157131</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.14395101553249498</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.17165277209694127</v>
+      <c r="D9" s="26">
+        <v>6.9574950200749136E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>9.62609054798029E-2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.12121137305437887</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.14263788093026122</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.17027750848134224</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -7074,29 +7281,29 @@
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -7106,30 +7313,30 @@
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>3.5585309134212512E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>4.7669006959134307E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>5.9136942047686603E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>6.8244113558733568E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>8.16617612035377E-2</v>
+      <c r="D11" s="26">
+        <v>3.0245638753255095E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>4.0990198151368604E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>5.0898361475939263E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>5.8966783265550798E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <v>7.0709967377876423E-2</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -7138,30 +7345,30 @@
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>4.4583839902191294E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>6.0966146566547801E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>7.6589293418878199E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>8.9700398797990244E-2</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0.10696223333277163</v>
+      <c r="D12" s="28">
+        <v>3.934195026758841E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>5.443182848384788E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>6.8540355355082003E-2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>8.0656218964453005E-2</v>
+      </c>
+      <c r="H12" s="29">
+        <v>9.6285362059658361E-2</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -7170,15 +7377,31 @@
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -7186,15 +7409,31 @@
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+    <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="31">
+        <v>143.92726240135795</v>
+      </c>
+      <c r="D14" s="31">
+        <v>132.11670973315375</v>
+      </c>
+      <c r="E14" s="31">
+        <v>127.92109046707326</v>
+      </c>
+      <c r="F14" s="31">
+        <v>124.0520736562639</v>
+      </c>
+      <c r="G14" s="31">
+        <v>120.90145345369872</v>
+      </c>
+      <c r="H14" s="31">
+        <v>116.3158834287934</v>
+      </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
@@ -7203,15 +7442,31 @@
       <c r="N14" s="16"/>
       <c r="O14" s="8"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31">
+        <v>220.80578160069166</v>
+      </c>
+      <c r="D15" s="31">
+        <v>205.44323034178609</v>
+      </c>
+      <c r="E15" s="31">
+        <v>199.5508171286335</v>
+      </c>
+      <c r="F15" s="31">
+        <v>194.04160963452654</v>
+      </c>
+      <c r="G15" s="31">
+        <v>189.31051281601898</v>
+      </c>
+      <c r="H15" s="31">
+        <v>183.20752325145048</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -7226,7 +7481,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7249,7 +7504,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -7272,7 +7527,7 @@
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -7295,7 +7550,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -7318,7 +7573,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -7341,7 +7596,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7364,7 +7619,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -7387,7 +7642,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -7410,7 +7665,7 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -7432,7 +7687,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -7454,7 +7709,7 @@
       <c r="U25" s="15"/>
       <c r="V25" s="15"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -7476,7 +7731,7 @@
       <c r="U26" s="14"/>
       <c r="V26" s="14"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7492,7 +7747,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -7508,7 +7763,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -7524,7 +7779,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7540,7 +7795,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -7563,7 +7818,7 @@
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7579,7 +7834,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -7595,7 +7850,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -7611,7 +7866,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -7627,7 +7882,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -7643,7 +7898,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -7659,7 +7914,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -7675,7 +7930,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7691,7 +7946,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -7707,7 +7962,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -7723,7 +7978,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -7739,7 +7994,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -7755,7 +8010,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -7771,7 +8026,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -7787,7 +8042,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -7803,7 +8058,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -7819,7 +8074,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -7835,7 +8090,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -7851,7 +8106,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -7867,7 +8122,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -7883,7 +8138,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -7899,7 +8154,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -7915,7 +8170,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -7931,7 +8186,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -7947,7 +8202,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -7963,7 +8218,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -7979,7 +8234,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -7995,7 +8250,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -8011,7 +8266,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -8027,7 +8282,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -8043,7 +8298,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -8059,7 +8314,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -8075,7 +8330,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -8091,7 +8346,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -8107,7 +8362,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -8123,7 +8378,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -8139,7 +8394,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -8155,7 +8410,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -8171,7 +8426,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -8187,7 +8442,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -8203,7 +8458,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -8219,7 +8474,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -8235,7 +8490,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="16"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -8251,7 +8506,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="16"/>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
@@ -8267,7 +8522,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="16"/>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
@@ -8283,7 +8538,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="16"/>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -8299,7 +8554,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="16"/>
     </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
@@ -8315,7 +8570,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
@@ -8331,7 +8586,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="16"/>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -8361,36 +8616,36 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W98"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="5" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="5"/>
+    <col min="10" max="16384" width="10.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -8405,29 +8660,29 @@
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
     </row>
-    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="16"/>
@@ -8444,30 +8699,30 @@
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
     </row>
-    <row r="5" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="22">
-        <v>48.949325901782046</v>
-      </c>
-      <c r="D5" s="22">
-        <v>44.741628456110973</v>
-      </c>
-      <c r="E5" s="22">
-        <v>43.296610274885929</v>
-      </c>
-      <c r="F5" s="22">
-        <v>41.899715769556472</v>
-      </c>
-      <c r="G5" s="22">
-        <v>40.769772531577622</v>
-      </c>
-      <c r="H5" s="22">
-        <v>39.155070048738217</v>
+      <c r="C5" s="24">
+        <v>70.066910313406694</v>
+      </c>
+      <c r="D5" s="24">
+        <v>64.162909882115443</v>
+      </c>
+      <c r="E5" s="24">
+        <v>62.228125003088685</v>
+      </c>
+      <c r="F5" s="24">
+        <v>60.343190989050775</v>
+      </c>
+      <c r="G5" s="24">
+        <v>58.875201570943204</v>
+      </c>
+      <c r="H5" s="24">
+        <v>56.696330310925816</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -8483,30 +8738,30 @@
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
     </row>
-    <row r="6" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="22">
-        <v>75.026221645356188</v>
-      </c>
-      <c r="D6" s="22">
-        <v>70.12588619217901</v>
-      </c>
-      <c r="E6" s="22">
-        <v>68.361415154349785</v>
-      </c>
-      <c r="F6" s="22">
-        <v>66.664267400103242</v>
-      </c>
-      <c r="G6" s="22">
-        <v>65.254325693412028</v>
-      </c>
-      <c r="H6" s="22">
-        <v>63.381013457735008</v>
+      <c r="C6" s="24">
+        <v>98.045066992505184</v>
+      </c>
+      <c r="D6" s="24">
+        <v>91.397928463548297</v>
+      </c>
+      <c r="E6" s="24">
+        <v>89.120399487925667</v>
+      </c>
+      <c r="F6" s="24">
+        <v>86.913320824301465</v>
+      </c>
+      <c r="G6" s="24">
+        <v>85.144918308539317</v>
+      </c>
+      <c r="H6" s="24">
+        <v>82.688582113478219</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -8522,29 +8777,29 @@
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="16"/>
@@ -8561,30 +8816,30 @@
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
     </row>
-    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
-        <v>8.5960273571773285E-2</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.11548096981434275</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.14401853350076321</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.16710247218964541</v>
-      </c>
-      <c r="H8" s="25">
-        <v>0.2000896983279449</v>
+      <c r="D8" s="26">
+        <v>8.426232018627447E-2</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.11187570959323613</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.13877762385785361</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.15972887476275735</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.19082588261241676</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -8600,30 +8855,30 @@
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
     </row>
-    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="24">
-        <v>6.5314970495791824E-2</v>
-      </c>
-      <c r="E9" s="24">
-        <v>8.8833028571137257E-2</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.11145375659165313</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.13024640902397089</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.15521517587100789</v>
+      <c r="D9" s="26">
+        <v>6.7796766658999905E-2</v>
+      </c>
+      <c r="E9" s="26">
+        <v>9.1026175802008905E-2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.1135370346481038</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.13157366382290286</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.15662679775822738</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -8639,29 +8894,29 @@
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="16"/>
@@ -8678,30 +8933,30 @@
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
     </row>
-    <row r="11" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="24">
-        <v>2.6406172046682809E-2</v>
-      </c>
-      <c r="E11" s="24">
-        <v>3.5474646954086142E-2</v>
-      </c>
-      <c r="F11" s="24">
-        <v>4.4241112964313392E-2</v>
-      </c>
-      <c r="G11" s="24">
-        <v>5.1332277652438134E-2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>6.1465637314485559E-2</v>
+      <c r="D11" s="26">
+        <v>3.7051630533169656E-2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>4.9193725597885679E-2</v>
+      </c>
+      <c r="F11" s="26">
+        <v>6.1022972475542586E-2</v>
+      </c>
+      <c r="G11" s="26">
+        <v>7.0235607565819605E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <v>8.3909511191847905E-2</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -8717,30 +8972,30 @@
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
     </row>
-    <row r="12" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="28">
         <v>0</v>
       </c>
-      <c r="D12" s="26">
-        <v>3.0752948075243196E-2</v>
-      </c>
-      <c r="E12" s="26">
-        <v>4.1826207594946256E-2</v>
-      </c>
-      <c r="F12" s="26">
-        <v>5.2476967580881551E-2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>6.1325313680714755E-2</v>
-      </c>
-      <c r="H12" s="27">
-        <v>7.3081625970548139E-2</v>
+      <c r="D12" s="28">
+        <v>4.1715329079649553E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <v>5.6008377177361519E-2</v>
+      </c>
+      <c r="F12" s="28">
+        <v>6.9859301504675758E-2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>8.0957233730540548E-2</v>
+      </c>
+      <c r="H12" s="29">
+        <v>9.6372419116079341E-2</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -8756,29 +9011,29 @@
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="25" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="16"/>
@@ -8788,30 +9043,30 @@
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="31">
-        <v>144.30980313528721</v>
+        <v>192.53020745971455</v>
       </c>
       <c r="D14" s="31">
-        <v>131.90489297868919</v>
+        <v>176.30716547321424</v>
       </c>
       <c r="E14" s="31">
-        <v>127.64476711550739</v>
+        <v>170.99075388202604</v>
       </c>
       <c r="F14" s="31">
-        <v>123.52651691795934</v>
+        <v>165.81132274759577</v>
       </c>
       <c r="G14" s="31">
-        <v>120.1952782701797</v>
+        <v>161.77757406433412</v>
       </c>
       <c r="H14" s="31">
-        <v>115.4348981601825</v>
+        <v>155.79046069166284</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
@@ -8820,30 +9075,30 @@
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="31">
-        <v>221.18832233462092</v>
+        <v>269.40872665904828</v>
       </c>
       <c r="D15" s="31">
-        <v>206.74141358732152</v>
+        <v>251.14368608184657</v>
       </c>
       <c r="E15" s="31">
-        <v>201.53949377706763</v>
+        <v>244.88548054358631</v>
       </c>
       <c r="F15" s="31">
-        <v>196.53605289622197</v>
+        <v>238.82085872585841</v>
       </c>
       <c r="G15" s="31">
-        <v>192.37933763249995</v>
+        <v>233.96163342665437</v>
       </c>
       <c r="H15" s="31">
-        <v>186.85653798283957</v>
+        <v>227.2121005143199</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
@@ -8852,7 +9107,7 @@
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -8868,7 +9123,7 @@
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -8885,7 +9140,7 @@
       <c r="N17" s="16"/>
       <c r="O17" s="8"/>
     </row>
-    <row r="18" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -8908,7 +9163,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
     </row>
-    <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -8931,7 +9186,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -8954,7 +9209,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -8977,7 +9232,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -9000,7 +9255,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
-    <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -9023,7 +9278,7 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
-    <row r="24" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -9046,7 +9301,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
     </row>
-    <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -9069,7 +9324,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
     </row>
-    <row r="26" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -9092,7 +9347,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
     </row>
-    <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -9114,7 +9369,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
     </row>
-    <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -9136,7 +9391,7 @@
       <c r="U28" s="15"/>
       <c r="V28" s="15"/>
     </row>
-    <row r="29" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -9158,7 +9413,7 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
     </row>
-    <row r="30" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -9174,7 +9429,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -9190,7 +9445,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -9206,7 +9461,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -9222,7 +9477,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -9245,7 +9500,7 @@
       <c r="V34" s="11"/>
       <c r="W34" s="11"/>
     </row>
-    <row r="35" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -9261,7 +9516,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -9277,7 +9532,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -9293,7 +9548,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -9309,7 +9564,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -9325,7 +9580,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -9341,7 +9596,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -9364,7 +9619,7 @@
       <c r="V41" s="11"/>
       <c r="W41" s="11"/>
     </row>
-    <row r="42" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -9387,7 +9642,7 @@
       <c r="V42" s="11"/>
       <c r="W42" s="11"/>
     </row>
-    <row r="43" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -9410,7 +9665,7 @@
       <c r="V43" s="11"/>
       <c r="W43" s="11"/>
     </row>
-    <row r="44" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -9433,7 +9688,7 @@
       <c r="V44" s="11"/>
       <c r="W44" s="11"/>
     </row>
-    <row r="45" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -9456,7 +9711,7 @@
       <c r="V45" s="11"/>
       <c r="W45" s="11"/>
     </row>
-    <row r="46" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -9479,7 +9734,7 @@
       <c r="V46" s="11"/>
       <c r="W46" s="11"/>
     </row>
-    <row r="47" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -9502,7 +9757,7 @@
       <c r="V47" s="11"/>
       <c r="W47" s="11"/>
     </row>
-    <row r="48" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -9525,7 +9780,7 @@
       <c r="V48" s="11"/>
       <c r="W48" s="11"/>
     </row>
-    <row r="49" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -9548,7 +9803,7 @@
       <c r="V49" s="11"/>
       <c r="W49" s="11"/>
     </row>
-    <row r="50" spans="1:23" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -9571,7 +9826,7 @@
       <c r="V50" s="11"/>
       <c r="W50" s="11"/>
     </row>
-    <row r="51" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -9594,7 +9849,7 @@
       <c r="V51" s="11"/>
       <c r="W51" s="11"/>
     </row>
-    <row r="52" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -9617,7 +9872,7 @@
       <c r="V52" s="11"/>
       <c r="W52" s="11"/>
     </row>
-    <row r="53" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -9640,7 +9895,7 @@
       <c r="V53" s="11"/>
       <c r="W53" s="11"/>
     </row>
-    <row r="54" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -9663,7 +9918,7 @@
       <c r="V54" s="11"/>
       <c r="W54" s="11"/>
     </row>
-    <row r="55" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -9686,7 +9941,7 @@
       <c r="V55" s="11"/>
       <c r="W55" s="11"/>
     </row>
-    <row r="56" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -9709,7 +9964,7 @@
       <c r="V56" s="11"/>
       <c r="W56" s="11"/>
     </row>
-    <row r="57" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -9732,7 +9987,7 @@
       <c r="V57" s="11"/>
       <c r="W57" s="11"/>
     </row>
-    <row r="58" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -9755,7 +10010,7 @@
       <c r="V58" s="11"/>
       <c r="W58" s="11"/>
     </row>
-    <row r="59" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -9778,7 +10033,7 @@
       <c r="V59" s="12"/>
       <c r="W59" s="12"/>
     </row>
-    <row r="60" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -9801,7 +10056,7 @@
       <c r="V60" s="13"/>
       <c r="W60" s="13"/>
     </row>
-    <row r="61" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -9817,7 +10072,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -9833,7 +10088,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -9849,7 +10104,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -9865,7 +10120,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -9882,7 +10137,7 @@
       <c r="N65" s="16"/>
       <c r="O65" s="8"/>
     </row>
-    <row r="66" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -9905,7 +10160,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -9928,7 +10183,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -9951,7 +10206,7 @@
       <c r="U68" s="11"/>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -9974,7 +10229,7 @@
       <c r="U69" s="11"/>
       <c r="V69" s="11"/>
     </row>
-    <row r="70" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -9997,7 +10252,7 @@
       <c r="U70" s="11"/>
       <c r="V70" s="11"/>
     </row>
-    <row r="71" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -10020,7 +10275,7 @@
       <c r="U71" s="11"/>
       <c r="V71" s="11"/>
     </row>
-    <row r="72" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -10043,7 +10298,7 @@
       <c r="U72" s="11"/>
       <c r="V72" s="11"/>
     </row>
-    <row r="73" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -10066,7 +10321,7 @@
       <c r="U73" s="11"/>
       <c r="V73" s="11"/>
     </row>
-    <row r="74" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -10089,7 +10344,7 @@
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
@@ -10111,7 +10366,7 @@
       <c r="U75" s="11"/>
       <c r="V75" s="11"/>
     </row>
-    <row r="76" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
@@ -10133,7 +10388,7 @@
       <c r="U76" s="15"/>
       <c r="V76" s="15"/>
     </row>
-    <row r="77" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -10155,7 +10410,7 @@
       <c r="U77" s="14"/>
       <c r="V77" s="14"/>
     </row>
-    <row r="78" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
@@ -10171,7 +10426,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
@@ -10187,7 +10442,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="16"/>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -10203,7 +10458,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -10219,7 +10474,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
@@ -10242,7 +10497,7 @@
       <c r="V82" s="11"/>
       <c r="W82" s="11"/>
     </row>
-    <row r="83" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="16"/>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
@@ -10258,7 +10513,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="16"/>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -10274,7 +10529,7 @@
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -10290,7 +10545,7 @@
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -10306,7 +10561,7 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -10322,7 +10577,7 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -10338,7 +10593,7 @@
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -10354,7 +10609,7 @@
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -10370,7 +10625,7 @@
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -10386,7 +10641,7 @@
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -10402,7 +10657,7 @@
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -10418,7 +10673,7 @@
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -10434,7 +10689,7 @@
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -10450,7 +10705,7 @@
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -10466,7 +10721,7 @@
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -10482,7 +10737,7 @@
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
